--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133697709</v>
       </c>
       <c r="B2" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>133697813</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>133697884</v>
       </c>
       <c r="B4" t="n">
-        <v>81341</v>
+        <v>81348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -675,44 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133697709</v>
+        <v>133697884</v>
       </c>
       <c r="B2" t="n">
-        <v>93264</v>
+        <v>81355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -721,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325728</v>
+        <v>325827</v>
       </c>
       <c r="R2" t="n">
-        <v>6557156</v>
+        <v>6557077</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133697813</v>
+        <v>133697709</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +811,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -835,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325824</v>
+        <v>325728</v>
       </c>
       <c r="R3" t="n">
-        <v>6557161</v>
+        <v>6557156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,36 +890,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133697884</v>
+        <v>133697813</v>
       </c>
       <c r="B4" t="n">
-        <v>81348</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325827</v>
+        <v>325824</v>
       </c>
       <c r="R4" t="n">
-        <v>6557077</v>
+        <v>6557161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697884</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697709</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>